--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260831.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>133,635</t>
+          <t>134,425</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.24%</t>
+          <t>27.42%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>96,880</t>
+          <t>97,450</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.07%</t>
+          <t>8.00%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,225</t>
+          <t>15,325</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>7.58%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>49,275</t>
+          <t>49,565</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.89%</t>
+          <t>5.78%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>117,245</t>
+          <t>117,945</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.30%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>57,740</t>
+          <t>58,080</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>4.73%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>63,255</t>
+          <t>63,705</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>17,813</t>
+          <t>17,913</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.95%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,115</t>
+          <t>19,225</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>43,655</t>
+          <t>43,915</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>74,565</t>
+          <t>75,005</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,460</t>
+          <t>30,640</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19,565</t>
+          <t>19,685</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
@@ -919,144 +919,144 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>49,255</t>
+          <t>49,545</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>25,608</t>
+          <t>99,741,356</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>34,920</t>
+          <t>25,758</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>18,920</t>
+          <t>35,130</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>57,388</t>
+          <t>19,030</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>11,351</t>
+          <t>57,728</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>72,515,261</t>
+          <t>11,351</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,690</t>
+          <t>7,790</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>20,688</t>
+          <t>20,808</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1117,78 +1117,78 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,336</t>
+          <t>9,436</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>122,585</t>
+          <t>17,955</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,845</t>
+          <t>15,571</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,471</t>
+          <t>123,305</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,967</t>
+          <t>19,077</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,670</t>
+          <t>41,920</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>36,130</t>
+          <t>36,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,315</t>
+          <t>11,415</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>346,257</t>
+          <t>210,236</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>263,979</t>
+          <t>348,008</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
